--- a/J30/Output_files/oLPN_Search_Result.xlsx
+++ b/J30/Output_files/oLPN_Search_Result.xlsx
@@ -498,12 +498,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>00008884070000210891</t>
+          <t>00008884070000228322</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>vgana3</t>
+          <t>praman</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -513,7 +513,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>706510-306-S/M</t>
+          <t>AR4999-101-L</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -521,42 +521,42 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>142100006086</t>
+          <t>367100018375</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>3301052101</t>
+          <t>3301002103</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>ZOZO</t>
+          <t>DIG</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>W04232026000000000010</t>
+          <t>W06152026000000000008</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>PLUS</t>
+          <t>SAGA</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0576443200</t>
+          <t>0171274294</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>810001860</t>
+          <t>810002632</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>0429_ＺＯＺＯ_AP_8887</t>
+          <t>0619_SAGA_H_71_E_09162</t>
         </is>
       </c>
     </row>
